--- a/Paper2_Package/03_RESULTS/Task3_druggability/task3_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task3_druggability/task3_supporting.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,26 @@
           <t>fisher_p</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>percent_excluding_classic_usable</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>background_excluding_classic_usable</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>odds_ratio_usable</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fisher_p_usable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +499,20 @@
           <t>2.192e-01</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8.833e-02</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,6 +540,20 @@
           <t>1.095e-08</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8.738e-04</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -533,6 +581,20 @@
           <t>9.708e-05</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.669e-03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +622,20 @@
           <t>3.872e-01</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2.937e-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -587,6 +663,20 @@
           <t>3.938e-07</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.709</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.111e-08</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,6 +704,20 @@
           <t>3.431e-08</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6.587e-04</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -639,6 +743,20 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>3.223e-01</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7.190e-01</t>
         </is>
       </c>
     </row>

--- a/Paper2_Package/03_RESULTS/Task3_druggability/task3_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task3_druggability/task3_supporting.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="classic_druggable_sensitivity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="classic_family_share" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,4 +764,129 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>drug_connected_genes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>classic_family_genes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>percent_classic_family</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>therapeutic action</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>decreasing</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>320</v>
+      </c>
+      <c r="D2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>therapeutic action</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>increasing</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>633</v>
+      </c>
+      <c r="D3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>entity-filtered</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>decreasing</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>244</v>
+      </c>
+      <c r="D4" t="n">
+        <v>61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>entity-filtered</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>increasing</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>540</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>